--- a/data/trans_orig/P2A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100887</t>
+          <t>101479</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133644</t>
+          <t>133785</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119788</t>
+          <t>118485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152581</t>
+          <t>152272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>228735</t>
+          <t>230194</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277200</t>
+          <t>276846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139366</t>
+          <t>139225</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172123</t>
+          <t>171531</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108257</t>
+          <t>108566</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141050</t>
+          <t>142353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>256648</t>
+          <t>257002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>305113</t>
+          <t>303654</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,88%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>208036</t>
+          <t>209552</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>251658</t>
+          <t>253088</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>308974</t>
+          <t>309630</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>350884</t>
+          <t>350739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>531532</t>
+          <t>530208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>591631</t>
+          <t>591571</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>241417</t>
+          <t>239987</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>285039</t>
+          <t>283523</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153065</t>
+          <t>153210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>194975</t>
+          <t>194319</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>405393</t>
+          <t>405453</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>465492</t>
+          <t>466816</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,82%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124645</t>
+          <t>125899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160024</t>
+          <t>161273</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210147</t>
+          <t>211727</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>245189</t>
+          <t>246608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344685</t>
+          <t>343826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>395700</t>
+          <t>395723</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>158822</t>
+          <t>157573</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>194201</t>
+          <t>192947</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90223</t>
+          <t>88804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125265</t>
+          <t>123685</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>258558</t>
+          <t>258535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>309573</t>
+          <t>310432</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>167195</t>
+          <t>167417</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>206839</t>
+          <t>203479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>240960</t>
+          <t>240194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>277355</t>
+          <t>275013</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>419244</t>
+          <t>417989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>470708</t>
+          <t>470556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151832</t>
+          <t>155192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191476</t>
+          <t>191254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94101</t>
+          <t>96443</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130496</t>
+          <t>131262</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>259419</t>
+          <t>259571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310883</t>
+          <t>312138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86767</t>
+          <t>87056</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114843</t>
+          <t>115767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121819</t>
+          <t>122109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149655</t>
+          <t>151397</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>216155</t>
+          <t>216437</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>257031</t>
+          <t>256876</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,5%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88465</t>
+          <t>87541</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116541</t>
+          <t>116252</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58013</t>
+          <t>56271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85849</t>
+          <t>85559</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153945</t>
+          <t>154100</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194821</t>
+          <t>194539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,34%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>121104</t>
+          <t>121513</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>153717</t>
+          <t>154950</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>162153</t>
+          <t>163005</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194944</t>
+          <t>195735</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>295246</t>
+          <t>294468</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>341664</t>
+          <t>339795</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>117094</t>
+          <t>115861</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149707</t>
+          <t>149298</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83200</t>
+          <t>82409</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115991</t>
+          <t>115139</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>207291</t>
+          <t>209160</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>253709</t>
+          <t>254487</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,36%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>254160</t>
+          <t>255317</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>306352</t>
+          <t>303556</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>370468</t>
+          <t>367425</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>417567</t>
+          <t>415884</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>636636</t>
+          <t>635718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>712527</t>
+          <t>707658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,47%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>308675</t>
+          <t>311471</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>360867</t>
+          <t>359710</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>220652</t>
+          <t>222335</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>267751</t>
+          <t>270794</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>540719</t>
+          <t>545588</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>616610</t>
+          <t>617528</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,27%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>355303</t>
+          <t>351035</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>411049</t>
+          <t>407446</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>469728</t>
+          <t>471141</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>523918</t>
+          <t>522999</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>839196</t>
+          <t>839313</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>917622</t>
+          <t>917815</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>332746</t>
+          <t>336349</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>388492</t>
+          <t>392760</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>259593</t>
+          <t>260512</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>313783</t>
+          <t>312370</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>609684</t>
+          <t>609491</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>688110</t>
+          <t>687993</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1519872</t>
+          <t>1520616</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1638673</t>
+          <t>1636835</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2100896</t>
+          <t>2105314</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2222608</t>
+          <t>2214989</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3652324</t>
+          <t>3655098</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3821214</t>
+          <t>3821684</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,42%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1637870</t>
+          <t>1639708</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1756671</t>
+          <t>1755927</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1156589</t>
+          <t>1164208</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1278301</t>
+          <t>1273883</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2834527</t>
+          <t>2834057</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3003417</t>
+          <t>3000643</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,08%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>161880</t>
+          <t>164102</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>196639</t>
+          <t>195984</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>210924</t>
+          <t>210715</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>239520</t>
+          <t>238946</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>380820</t>
+          <t>381862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>426898</t>
+          <t>429275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,76%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98099</t>
+          <t>98754</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132858</t>
+          <t>130636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47725</t>
+          <t>48299</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76321</t>
+          <t>76530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155085</t>
+          <t>152708</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>201163</t>
+          <t>200121</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>243428</t>
+          <t>243857</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>292439</t>
+          <t>289676</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>344534</t>
+          <t>346788</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>388920</t>
+          <t>387995</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601793</t>
+          <t>598029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>670152</t>
+          <t>662873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>213088</t>
+          <t>215851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>262099</t>
+          <t>261670</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134845</t>
+          <t>135770</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>179231</t>
+          <t>176977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>359140</t>
+          <t>366419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>427499</t>
+          <t>431263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171872</t>
+          <t>175546</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>208827</t>
+          <t>210782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>214126</t>
+          <t>215879</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>250052</t>
+          <t>251722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>401395</t>
+          <t>400464</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>452247</t>
+          <t>450289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,71%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115219</t>
+          <t>113264</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>152174</t>
+          <t>148500</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90968</t>
+          <t>89298</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>126894</t>
+          <t>125141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212819</t>
+          <t>214777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>263671</t>
+          <t>264602</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>199818</t>
+          <t>201353</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>239794</t>
+          <t>241055</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>259504</t>
+          <t>257960</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>294440</t>
+          <t>296817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>469575</t>
+          <t>470839</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>523689</t>
+          <t>523798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134188</t>
+          <t>132927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174164</t>
+          <t>172629</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>94511</t>
+          <t>92134</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129447</t>
+          <t>130991</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>239244</t>
+          <t>239135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>293358</t>
+          <t>292094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,29%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>105286</t>
+          <t>103894</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134787</t>
+          <t>135658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>169240</t>
+          <t>168200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>190859</t>
+          <t>191825</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>282244</t>
+          <t>280342</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>319435</t>
+          <t>318746</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>73,75%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77831</t>
+          <t>76960</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107332</t>
+          <t>108724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28732</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50351</t>
+          <t>51391</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112774</t>
+          <t>113463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149965</t>
+          <t>151867</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>154564</t>
+          <t>153701</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>188653</t>
+          <t>186613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>202212</t>
+          <t>202680</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>230049</t>
+          <t>230178</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>366035</t>
+          <t>367176</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>410185</t>
+          <t>410371</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,07%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85328</t>
+          <t>87368</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>119417</t>
+          <t>120280</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49982</t>
+          <t>49853</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77819</t>
+          <t>77351</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>143827</t>
+          <t>143641</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>187977</t>
+          <t>186836</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>354532</t>
+          <t>351832</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>408884</t>
+          <t>408110</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>449463</t>
+          <t>451801</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>503226</t>
+          <t>501220</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>825445</t>
+          <t>825504</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>898623</t>
+          <t>893853</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>253904</t>
+          <t>254678</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>308256</t>
+          <t>310956</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>190627</t>
+          <t>192633</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>244390</t>
+          <t>242052</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>458018</t>
+          <t>462788</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>531196</t>
+          <t>531137</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>340412</t>
+          <t>341493</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>402278</t>
+          <t>399427</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>454511</t>
+          <t>452708</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>512169</t>
+          <t>511626</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>815487</t>
+          <t>812859</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>897776</t>
+          <t>893518</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,74%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>376820</t>
+          <t>379671</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>438686</t>
+          <t>437605</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>311684</t>
+          <t>312227</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>369342</t>
+          <t>371145</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>705175</t>
+          <t>709433</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>787464</t>
+          <t>790092</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1849476</t>
+          <t>1850019</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1968067</t>
+          <t>1965044</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2403543</t>
+          <t>2409124</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2519341</t>
+          <t>2519358</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4285196</t>
+          <t>4292739</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4452118</t>
+          <t>4457638</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,82%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1458712</t>
+          <t>1461735</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1577303</t>
+          <t>1576760</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1038968</t>
+          <t>1038951</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1154766</t>
+          <t>1149185</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2532970</t>
+          <t>2527450</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2699892</t>
+          <t>2692349</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148806</t>
+          <t>148705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>184454</t>
+          <t>184369</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>182796</t>
+          <t>183685</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>213246</t>
+          <t>213695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>343331</t>
+          <t>337292</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>391090</t>
+          <t>386717</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,39%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109307</t>
+          <t>109392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144955</t>
+          <t>145056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75457</t>
+          <t>75008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105907</t>
+          <t>105018</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>191374</t>
+          <t>195747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239133</t>
+          <t>245172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>265080</t>
+          <t>264295</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311997</t>
+          <t>311548</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>349832</t>
+          <t>350906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>392340</t>
+          <t>392061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>630108</t>
+          <t>627160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>691916</t>
+          <t>690239</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,3%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>190578</t>
+          <t>191027</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>237495</t>
+          <t>238280</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130744</t>
+          <t>131023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173252</t>
+          <t>172178</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>333743</t>
+          <t>335420</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>395551</t>
+          <t>398499</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151825</t>
+          <t>151698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>184234</t>
+          <t>185695</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187049</t>
+          <t>190638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>223280</t>
+          <t>225084</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>351341</t>
+          <t>351070</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>400950</t>
+          <t>399632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,02%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134331</t>
+          <t>132870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166740</t>
+          <t>166867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113029</t>
+          <t>111225</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149260</t>
+          <t>145671</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>253924</t>
+          <t>255242</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>303533</t>
+          <t>303804</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>198023</t>
+          <t>196620</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234397</t>
+          <t>234223</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>257448</t>
+          <t>255688</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>293493</t>
+          <t>292248</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>463002</t>
+          <t>464537</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>516493</t>
+          <t>519974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135567</t>
+          <t>135741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>171941</t>
+          <t>173344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93790</t>
+          <t>95035</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129835</t>
+          <t>131595</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>240754</t>
+          <t>237273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>294245</t>
+          <t>292710</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96460</t>
+          <t>95408</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126195</t>
+          <t>124672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126510</t>
+          <t>125845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154204</t>
+          <t>153846</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>231795</t>
+          <t>234173</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>271705</t>
+          <t>274544</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,88%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>85026</t>
+          <t>86549</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114761</t>
+          <t>115813</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64383</t>
+          <t>64741</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92077</t>
+          <t>92742</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>158103</t>
+          <t>155264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198013</t>
+          <t>195635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>114309</t>
+          <t>113873</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147689</t>
+          <t>146845</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>152067</t>
+          <t>154797</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>184219</t>
+          <t>186511</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>277205</t>
+          <t>273462</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>323288</t>
+          <t>320931</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115434</t>
+          <t>116278</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148814</t>
+          <t>149250</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>88896</t>
+          <t>86604</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121048</t>
+          <t>118318</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>212950</t>
+          <t>215307</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>259033</t>
+          <t>262776</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>265799</t>
+          <t>260988</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>322522</t>
+          <t>317096</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>365494</t>
+          <t>364706</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>419435</t>
+          <t>417684</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>645652</t>
+          <t>646903</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>725579</t>
+          <t>722171</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>334036</t>
+          <t>339462</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>390759</t>
+          <t>395570</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>271859</t>
+          <t>273610</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>325800</t>
+          <t>326588</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>622273</t>
+          <t>625681</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>702200</t>
+          <t>700949</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>373470</t>
+          <t>370497</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>427455</t>
+          <t>428739</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>477427</t>
+          <t>476762</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>533370</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>867657</t>
+          <t>861401</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>945322</t>
+          <t>943641</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,8%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>351128</t>
+          <t>349844</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>405113</t>
+          <t>408086</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>292797</t>
+          <t>292361</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>348740</t>
+          <t>349405</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>659428</t>
+          <t>661109</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>737093</t>
+          <t>743349</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1712701</t>
+          <t>1714718</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1832928</t>
+          <t>1829476</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2202021</t>
+          <t>2204921</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2314803</t>
+          <t>2318325</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3949120</t>
+          <t>3954961</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4116959</t>
+          <t>4114052</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1561422</t>
+          <t>1564874</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1681649</t>
+          <t>1679632</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1229739</t>
+          <t>1226217</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1342521</t>
+          <t>1339621</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2821933</t>
+          <t>2824840</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2989772</t>
+          <t>2983931</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>182235</t>
+          <t>180550</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>220788</t>
+          <t>220379</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191234</t>
+          <t>191661</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>216126</t>
+          <t>217451</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>382105</t>
+          <t>381129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>430001</t>
+          <t>427761</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90655</t>
+          <t>91064</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129208</t>
+          <t>130893</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73509</t>
+          <t>72184</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98401</t>
+          <t>97974</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171076</t>
+          <t>173316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>218972</t>
+          <t>219948</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>182810</t>
+          <t>181127</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>239029</t>
+          <t>237614</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>216796</t>
+          <t>214135</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>256500</t>
+          <t>254135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>407324</t>
+          <t>409034</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>477595</t>
+          <t>481956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>279361</t>
+          <t>280776</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335580</t>
+          <t>337263</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>258469</t>
+          <t>260834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>298173</t>
+          <t>300834</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>555764</t>
+          <t>551403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>626035</t>
+          <t>624325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135963</t>
+          <t>137552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>171711</t>
+          <t>171832</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162748</t>
+          <t>162508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195022</t>
+          <t>194375</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>309735</t>
+          <t>305939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>356503</t>
+          <t>355663</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144339</t>
+          <t>144218</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180087</t>
+          <t>178498</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154106</t>
+          <t>154753</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186380</t>
+          <t>186620</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308675</t>
+          <t>309515</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>355443</t>
+          <t>359239</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>54,01%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>119321</t>
+          <t>117485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162324</t>
+          <t>160152</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115696</t>
+          <t>117476</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>243908</t>
+          <t>245674</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>243085</t>
+          <t>242747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>386320</t>
+          <t>385896</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150233</t>
+          <t>152405</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>193236</t>
+          <t>195072</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231810</t>
+          <t>230044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>360022</t>
+          <t>358242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>401954</t>
+          <t>402378</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>545189</t>
+          <t>545527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,21%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17011</t>
+          <t>16809</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31179</t>
+          <t>31164</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20405</t>
+          <t>21037</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50076</t>
+          <t>50422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41729</t>
+          <t>41809</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75380</t>
+          <t>75012</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147563</t>
+          <t>147578</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161731</t>
+          <t>161933</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208703</t>
+          <t>208357</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>238374</t>
+          <t>237742</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>362141</t>
+          <t>362509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>395792</t>
+          <t>395712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,44%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>138780</t>
+          <t>140006</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>169115</t>
+          <t>171464</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>134668</t>
+          <t>135447</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159944</t>
+          <t>160308</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>284223</t>
+          <t>282652</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>323465</t>
+          <t>322465</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,22%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>100521</t>
+          <t>98172</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>130856</t>
+          <t>129630</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97112</t>
+          <t>96748</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122388</t>
+          <t>121609</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>203227</t>
+          <t>204227</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>242469</t>
+          <t>244040</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,33%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180304</t>
+          <t>181787</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>235440</t>
+          <t>231291</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,47 +12775,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>37,05%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>456895</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>320285</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>652332</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>53,8%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>37,71%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>456895</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>321544</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>634828</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>53,8%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>37,86%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>523696</t>
+          <t>516974</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>982054</t>
+          <t>948564</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>64,37%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>388839</t>
+          <t>392988</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>443975</t>
+          <t>442492</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,49 +12888,49 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>62,95%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>70,88%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>392370</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>196933</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>528980</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>46,2%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>23,19%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>62,29%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>71,12%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>392370</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>214437</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>527721</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>46,2%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>25,25%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>62,14%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>955</t>
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>491490</t>
+          <t>524980</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>949848</t>
+          <t>956570</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>101941</t>
+          <t>99846</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>321602</t>
+          <t>322235</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>299841</t>
+          <t>301418</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>347069</t>
+          <t>345404</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>340114</t>
+          <t>334433</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>662278</t>
+          <t>661441</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,17%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>607118</t>
+          <t>606485</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>826779</t>
+          <t>828874</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>370662</t>
+          <t>372327</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>417890</t>
+          <t>416313</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>984174</t>
+          <t>985011</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1306338</t>
+          <t>1312019</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1045718</t>
+          <t>1022275</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1448031</t>
+          <t>1443659</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1639887</t>
+          <t>1633608</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2155738</t>
+          <t>2158123</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2816485</t>
+          <t>2822782</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3464703</t>
+          <t>3424282</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2011786</t>
+          <t>2016158</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2414099</t>
+          <t>2437542</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1556542</t>
+          <t>1554157</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2072393</t>
+          <t>2078672</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3707394</t>
+          <t>3747815</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4355612</t>
+          <t>4349315</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>101479</t>
+          <t>101934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133785</t>
+          <t>134651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118485</t>
+          <t>119762</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152272</t>
+          <t>152517</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>230194</t>
+          <t>229313</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>276846</t>
+          <t>276193</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139225</t>
+          <t>138359</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>171531</t>
+          <t>171076</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108566</t>
+          <t>108321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142353</t>
+          <t>141076</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257002</t>
+          <t>257655</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>303654</t>
+          <t>304535</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,05%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>209552</t>
+          <t>209103</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>253088</t>
+          <t>254418</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>309630</t>
+          <t>309018</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>350739</t>
+          <t>351222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>530208</t>
+          <t>530743</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>591571</t>
+          <t>592652</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>239987</t>
+          <t>238657</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>283523</t>
+          <t>283972</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153210</t>
+          <t>152727</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>194319</t>
+          <t>194931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>405453</t>
+          <t>404372</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>466816</t>
+          <t>466281</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125899</t>
+          <t>122777</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161273</t>
+          <t>160557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>211727</t>
+          <t>210473</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>246608</t>
+          <t>245076</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>343826</t>
+          <t>344552</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>395723</t>
+          <t>395968</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>157573</t>
+          <t>158289</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>192947</t>
+          <t>196069</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88804</t>
+          <t>90336</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123685</t>
+          <t>124939</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>258535</t>
+          <t>258290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>310432</t>
+          <t>309706</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,34%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>167417</t>
+          <t>168367</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>203479</t>
+          <t>204835</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>240194</t>
+          <t>241034</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275013</t>
+          <t>275601</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>417989</t>
+          <t>418486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>470556</t>
+          <t>472507</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155192</t>
+          <t>153836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191254</t>
+          <t>190304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96443</t>
+          <t>95855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131262</t>
+          <t>130422</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>259571</t>
+          <t>257620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312138</t>
+          <t>311641</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,68%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87056</t>
+          <t>88158</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115767</t>
+          <t>116744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>122109</t>
+          <t>122847</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151397</t>
+          <t>149657</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>216437</t>
+          <t>216904</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256876</t>
+          <t>257918</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87541</t>
+          <t>86564</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116252</t>
+          <t>115150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56271</t>
+          <t>58011</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85559</t>
+          <t>84821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154100</t>
+          <t>153058</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>194539</t>
+          <t>194072</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>121513</t>
+          <t>121949</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>154950</t>
+          <t>153344</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>163005</t>
+          <t>162428</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>195735</t>
+          <t>194003</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>294468</t>
+          <t>294312</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>339795</t>
+          <t>340643</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,05%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115861</t>
+          <t>117467</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149298</t>
+          <t>148862</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82409</t>
+          <t>84141</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115139</t>
+          <t>115716</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>209160</t>
+          <t>208312</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>254487</t>
+          <t>254643</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>255317</t>
+          <t>252847</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>303556</t>
+          <t>305044</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>367425</t>
+          <t>366353</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>415884</t>
+          <t>415770</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>635718</t>
+          <t>635697</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>707658</t>
+          <t>708604</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>311471</t>
+          <t>309983</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>359710</t>
+          <t>362180</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>222335</t>
+          <t>222449</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>270794</t>
+          <t>271866</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>545588</t>
+          <t>544642</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>617528</t>
+          <t>617549</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>351035</t>
+          <t>353118</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>407446</t>
+          <t>410541</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>471141</t>
+          <t>465868</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>522999</t>
+          <t>523013</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>839313</t>
+          <t>836993</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>917815</t>
+          <t>914949</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>336349</t>
+          <t>333254</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>392760</t>
+          <t>390677</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>260512</t>
+          <t>260498</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>312370</t>
+          <t>317643</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>609491</t>
+          <t>612357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>687993</t>
+          <t>690313</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1520616</t>
+          <t>1523547</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1636835</t>
+          <t>1639290</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2105314</t>
+          <t>2098769</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2214989</t>
+          <t>2211245</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3655098</t>
+          <t>3649928</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3821684</t>
+          <t>3815091</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,32%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1639708</t>
+          <t>1637253</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1755927</t>
+          <t>1752996</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1164208</t>
+          <t>1167952</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1273883</t>
+          <t>1280428</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2834057</t>
+          <t>2840650</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3000643</t>
+          <t>3005813</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164102</t>
+          <t>162868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>195984</t>
+          <t>196500</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>210715</t>
+          <t>211275</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>238946</t>
+          <t>239190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>381862</t>
+          <t>382440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>429275</t>
+          <t>427313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,42%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98754</t>
+          <t>98238</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130636</t>
+          <t>131870</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48299</t>
+          <t>48055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76530</t>
+          <t>75970</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>152708</t>
+          <t>154670</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200121</t>
+          <t>199543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>243857</t>
+          <t>243478</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>289676</t>
+          <t>289442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>346788</t>
+          <t>345785</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>387995</t>
+          <t>389166</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>598029</t>
+          <t>601447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>662873</t>
+          <t>667159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>215851</t>
+          <t>216085</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>261670</t>
+          <t>262049</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135770</t>
+          <t>134599</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176977</t>
+          <t>177980</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>366419</t>
+          <t>362133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>431263</t>
+          <t>427845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,57%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>175546</t>
+          <t>175994</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>210782</t>
+          <t>211687</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>215879</t>
+          <t>213868</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>251722</t>
+          <t>250615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>400464</t>
+          <t>402179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>450289</t>
+          <t>451761</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113264</t>
+          <t>112359</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148500</t>
+          <t>148052</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89298</t>
+          <t>90405</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125141</t>
+          <t>127152</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>214777</t>
+          <t>213305</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>264602</t>
+          <t>262887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>201353</t>
+          <t>201125</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>241055</t>
+          <t>239855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>257960</t>
+          <t>257283</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>296817</t>
+          <t>293806</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>470839</t>
+          <t>470897</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>523798</t>
+          <t>524259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>132927</t>
+          <t>134127</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172629</t>
+          <t>172857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92134</t>
+          <t>95145</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130991</t>
+          <t>131668</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>239135</t>
+          <t>238674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>292094</t>
+          <t>292036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>103894</t>
+          <t>104701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135658</t>
+          <t>134213</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>168200</t>
+          <t>168371</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>191825</t>
+          <t>190606</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>280342</t>
+          <t>279490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>318746</t>
+          <t>319544</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76960</t>
+          <t>78405</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108724</t>
+          <t>107917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27766</t>
+          <t>28985</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51391</t>
+          <t>51220</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113463</t>
+          <t>112665</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>151867</t>
+          <t>152719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>153701</t>
+          <t>156361</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>186613</t>
+          <t>190032</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>202680</t>
+          <t>201594</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>230178</t>
+          <t>230203</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>367176</t>
+          <t>363164</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>410371</t>
+          <t>409026</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,83%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87368</t>
+          <t>83949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120280</t>
+          <t>117620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49853</t>
+          <t>49828</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77351</t>
+          <t>78437</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>143641</t>
+          <t>144986</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>186836</t>
+          <t>190848</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>351832</t>
+          <t>355764</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>408110</t>
+          <t>409978</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>451801</t>
+          <t>453780</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>501220</t>
+          <t>503582</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>825504</t>
+          <t>822096</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>893853</t>
+          <t>891768</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,73%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>254678</t>
+          <t>252810</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>310956</t>
+          <t>307024</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>192633</t>
+          <t>190271</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>242052</t>
+          <t>240073</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>462788</t>
+          <t>464873</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>531137</t>
+          <t>534545</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>341493</t>
+          <t>340795</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>399427</t>
+          <t>398923</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>452708</t>
+          <t>456240</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>511626</t>
+          <t>512507</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>812859</t>
+          <t>812333</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>893518</t>
+          <t>890324</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,54%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>379671</t>
+          <t>380175</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>437605</t>
+          <t>438303</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>312227</t>
+          <t>311346</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>371145</t>
+          <t>367613</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>709433</t>
+          <t>712627</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>790092</t>
+          <t>790618</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1850019</t>
+          <t>1844031</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1965044</t>
+          <t>1970458</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2409124</t>
+          <t>2401120</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2519358</t>
+          <t>2517117</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4292739</t>
+          <t>4284597</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4457638</t>
+          <t>4451431</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,73%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1461735</t>
+          <t>1456321</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1576760</t>
+          <t>1582748</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1038951</t>
+          <t>1041192</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1149185</t>
+          <t>1157189</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2527450</t>
+          <t>2533657</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2692349</t>
+          <t>2700491</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148705</t>
+          <t>146113</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>184369</t>
+          <t>182602</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183685</t>
+          <t>183629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>213695</t>
+          <t>215660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>337292</t>
+          <t>342626</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>386717</t>
+          <t>388795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,75%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109392</t>
+          <t>111159</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145056</t>
+          <t>147648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75008</t>
+          <t>73043</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105018</t>
+          <t>105074</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>195747</t>
+          <t>193669</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>245172</t>
+          <t>239838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>264295</t>
+          <t>267537</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311548</t>
+          <t>311300</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>350906</t>
+          <t>349622</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>392061</t>
+          <t>390777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>627160</t>
+          <t>630638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>690239</t>
+          <t>694251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191027</t>
+          <t>191275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>238280</t>
+          <t>235038</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>131023</t>
+          <t>132307</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172178</t>
+          <t>173462</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>335420</t>
+          <t>331408</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398499</t>
+          <t>395021</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151698</t>
+          <t>152074</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>185695</t>
+          <t>186496</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>190638</t>
+          <t>190870</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225084</t>
+          <t>226632</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>351070</t>
+          <t>349253</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>399632</t>
+          <t>399653</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>132870</t>
+          <t>132069</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166867</t>
+          <t>166491</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111225</t>
+          <t>109677</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145671</t>
+          <t>145439</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255242</t>
+          <t>255221</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>303804</t>
+          <t>305621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>196620</t>
+          <t>196851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234223</t>
+          <t>235501</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>255688</t>
+          <t>256656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>292248</t>
+          <t>293489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>464537</t>
+          <t>463645</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>519974</t>
+          <t>518245</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135741</t>
+          <t>134463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173344</t>
+          <t>173113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95035</t>
+          <t>93794</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131595</t>
+          <t>130627</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>237273</t>
+          <t>239002</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>292710</t>
+          <t>293602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95408</t>
+          <t>97243</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>124672</t>
+          <t>126601</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125845</t>
+          <t>127477</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>153846</t>
+          <t>155431</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>234173</t>
+          <t>230178</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>274544</t>
+          <t>270087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>62,84%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86549</t>
+          <t>84620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115813</t>
+          <t>113978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64741</t>
+          <t>63156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92742</t>
+          <t>91110</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155264</t>
+          <t>159721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>195635</t>
+          <t>199630</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>46,45%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>113873</t>
+          <t>114304</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>146845</t>
+          <t>146777</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>154797</t>
+          <t>150146</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>186511</t>
+          <t>183578</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>273462</t>
+          <t>276675</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>320931</t>
+          <t>322202</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116278</t>
+          <t>116346</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149250</t>
+          <t>148819</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86604</t>
+          <t>89537</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>118318</t>
+          <t>122969</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>215307</t>
+          <t>214036</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>262776</t>
+          <t>259563</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>260988</t>
+          <t>267880</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>317096</t>
+          <t>318903</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>364706</t>
+          <t>362685</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>417684</t>
+          <t>417160</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>646903</t>
+          <t>645696</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>722171</t>
+          <t>718717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>339462</t>
+          <t>337655</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>395570</t>
+          <t>388678</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>273610</t>
+          <t>274134</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326588</t>
+          <t>328609</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>625681</t>
+          <t>629135</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>700949</t>
+          <t>702156</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,09%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>370497</t>
+          <t>368645</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>428739</t>
+          <t>427949</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>476762</t>
+          <t>473911</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>533806</t>
+          <t>533505</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>861401</t>
+          <t>864671</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>943641</t>
+          <t>941364</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,66%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>349844</t>
+          <t>350634</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>408086</t>
+          <t>409938</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>292361</t>
+          <t>292662</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>349405</t>
+          <t>352256</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>661109</t>
+          <t>663386</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>743349</t>
+          <t>740079</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1714718</t>
+          <t>1708608</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1829476</t>
+          <t>1830690</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2204921</t>
+          <t>2200429</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2318325</t>
+          <t>2313834</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3954961</t>
+          <t>3947609</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4114052</t>
+          <t>4111313</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,25%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1564874</t>
+          <t>1563660</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1679632</t>
+          <t>1685742</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1226217</t>
+          <t>1230708</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1339621</t>
+          <t>1344113</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2824840</t>
+          <t>2827579</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2983931</t>
+          <t>2991283</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>201413</t>
+          <t>191271</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>180550</t>
+          <t>173542</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>220379</t>
+          <t>208958</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>204585</t>
+          <t>211079</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191661</t>
+          <t>196002</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>217451</t>
+          <t>224824</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>405997</t>
+          <t>402350</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>381129</t>
+          <t>378638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>427761</t>
+          <t>424939</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>66,93%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>110030</t>
+          <t>127574</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91064</t>
+          <t>109887</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>130893</t>
+          <t>145303</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85050</t>
+          <t>104982</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72184</t>
+          <t>91237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97974</t>
+          <t>120059</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>195080</t>
+          <t>232556</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173316</t>
+          <t>209967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>219948</t>
+          <t>256268</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>40,36%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>209116</t>
+          <t>210802</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>181127</t>
+          <t>184082</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>237614</t>
+          <t>239555</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>234843</t>
+          <t>246507</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>214135</t>
+          <t>224701</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>254135</t>
+          <t>267221</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>443959</t>
+          <t>457309</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>409034</t>
+          <t>423964</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>481956</t>
+          <t>493253</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>45,79%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>309274</t>
+          <t>319845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>280776</t>
+          <t>291092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>337263</t>
+          <t>346565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>280126</t>
+          <t>299987</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>260834</t>
+          <t>279273</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>300834</t>
+          <t>321793</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>589400</t>
+          <t>619832</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>551403</t>
+          <t>583888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>624325</t>
+          <t>653177</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>154192</t>
+          <t>152561</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>137552</t>
+          <t>134814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>171832</t>
+          <t>169500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>178378</t>
+          <t>181114</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162508</t>
+          <t>165236</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>194375</t>
+          <t>197030</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>332569</t>
+          <t>333676</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>305939</t>
+          <t>312129</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>355663</t>
+          <t>357474</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,17%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>161858</t>
+          <t>163432</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144218</t>
+          <t>146493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>178498</t>
+          <t>181179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>170750</t>
+          <t>175267</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154753</t>
+          <t>159351</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>186620</t>
+          <t>191145</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>332609</t>
+          <t>338699</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309515</t>
+          <t>314901</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>359239</t>
+          <t>360246</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>139789</t>
+          <t>165896</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117485</t>
+          <t>140188</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160152</t>
+          <t>189625</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>193728</t>
+          <t>216663</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117476</t>
+          <t>195407</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>245674</t>
+          <t>236956</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>333516</t>
+          <t>382560</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242747</t>
+          <t>348883</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>385896</t>
+          <t>414717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>172768</t>
+          <t>207249</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152405</t>
+          <t>183520</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>195072</t>
+          <t>232957</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>281990</t>
+          <t>205298</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>230044</t>
+          <t>185005</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358242</t>
+          <t>226554</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>454758</t>
+          <t>412547</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>402378</t>
+          <t>380390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>545527</t>
+          <t>446224</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23279</t>
+          <t>25319</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16809</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31164</t>
+          <t>33750</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38655</t>
+          <t>41267</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21037</t>
+          <t>33752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50422</t>
+          <t>49457</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>61934</t>
+          <t>66586</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41809</t>
+          <t>56333</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75012</t>
+          <t>78947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>155463</t>
+          <t>180346</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147578</t>
+          <t>171915</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161933</t>
+          <t>187004</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>220124</t>
+          <t>187651</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>208357</t>
+          <t>179461</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>237742</t>
+          <t>195166</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>375587</t>
+          <t>367996</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>362509</t>
+          <t>355635</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>395712</t>
+          <t>378249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>155020</t>
+          <t>155289</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>140006</t>
+          <t>141560</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>171464</t>
+          <t>169433</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>147720</t>
+          <t>149875</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>135447</t>
+          <t>136973</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>160308</t>
+          <t>162621</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>302741</t>
+          <t>305164</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>282652</t>
+          <t>284760</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>322465</t>
+          <t>324900</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,79%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>114616</t>
+          <t>115418</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98172</t>
+          <t>101274</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>129630</t>
+          <t>129147</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>109336</t>
+          <t>113875</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>96748</t>
+          <t>101129</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121609</t>
+          <t>126777</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>223951</t>
+          <t>229293</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204227</t>
+          <t>209557</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>244040</t>
+          <t>249697</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>206602</t>
+          <t>236790</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>181787</t>
+          <t>211378</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>231291</t>
+          <t>266316</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>456895</t>
+          <t>310667</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>320285</t>
+          <t>286607</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>652332</t>
+          <t>338455</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>663497</t>
+          <t>547457</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>516974</t>
+          <t>510205</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>948564</t>
+          <t>586910</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>417677</t>
+          <t>482897</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>392988</t>
+          <t>453371</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>442492</t>
+          <t>508309</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>392370</t>
+          <t>461390</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>196933</t>
+          <t>433602</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>528980</t>
+          <t>485450</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>810047</t>
+          <t>944287</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>524980</t>
+          <t>904834</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>956570</t>
+          <t>981539</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,8%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>229364</t>
+          <t>260054</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99846</t>
+          <t>235464</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>322235</t>
+          <t>289115</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>324014</t>
+          <t>371616</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>301418</t>
+          <t>347521</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>345404</t>
+          <t>399324</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>553378</t>
+          <t>631670</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>334433</t>
+          <t>595880</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>661441</t>
+          <t>670879</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>41,17%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>699356</t>
+          <t>538018</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>606485</t>
+          <t>508957</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>828874</t>
+          <t>562608</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>393717</t>
+          <t>459715</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>372327</t>
+          <t>432007</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>416313</t>
+          <t>483810</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1093074</t>
+          <t>997733</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>985011</t>
+          <t>958524</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1312019</t>
+          <t>1033523</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1318774</t>
+          <t>1397982</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1022275</t>
+          <t>1339425</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1443659</t>
+          <t>1464117</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1778817</t>
+          <t>1728788</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1633608</t>
+          <t>1679038</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2158123</t>
+          <t>1785648</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3097592</t>
+          <t>3126771</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2822782</t>
+          <t>3042214</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3424282</t>
+          <t>3215997</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2141043</t>
+          <t>2134780</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2016158</t>
+          <t>2068645</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2437542</t>
+          <t>2193337</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1933463</t>
+          <t>2008166</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1554157</t>
+          <t>1951306</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2078672</t>
+          <t>2057916</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4074505</t>
+          <t>4142945</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3747815</t>
+          <t>4053719</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4349315</t>
+          <t>4227502</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
